--- a/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179DC7D8-EEC3-4F07-A4AF-101509761D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13520"/>
+    <workbookView xWindow="1400" yWindow="1480" windowWidth="18440" windowHeight="13060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -150,19 +154,64 @@
   </si>
   <si>
     <t>L1_Shrimp</t>
+  </si>
+  <si>
+    <t>IconResName</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Cucumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	L1_Icon_Pumpkin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_ChickenLeg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Apple</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Broccoli</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Biscuit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Blueberry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Carrot</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Egg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Salmon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Shrimp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,137 +240,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,182 +288,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -523,331 +297,56 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1134,24 +633,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="3" customWidth="1"/>
     <col min="3" max="3" width="16" style="3" customWidth="1"/>
     <col min="4" max="4" width="15" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.6923076923077" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="4"/>
+    <col min="5" max="5" width="15.7265625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.8" spans="1:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1167,8 +667,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="16.8" spans="1:5">
+      <c r="F1" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1184,8 +687,11 @@
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="16.8" spans="1:4">
+      <c r="F2" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1199,11 +705,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="16.8" spans="2:5">
+    <row r="4" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="3">
         <v>4</v>
       </c>
       <c r="D4" s="4">
@@ -1212,12 +718,15 @@
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" ht="16.8" spans="2:5">
+      <c r="F4" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="3">
         <v>4</v>
       </c>
       <c r="D5" s="4">
@@ -1226,12 +735,15 @@
       <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="16.8" spans="2:5">
+      <c r="F5" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
       <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="3">
         <v>4</v>
       </c>
       <c r="D6" s="4">
@@ -1240,13 +752,16 @@
       <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" ht="16.8" spans="1:5">
-      <c r="A7" s="9"/>
+      <c r="F6" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
       <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="3">
         <v>4</v>
       </c>
       <c r="D7" s="4">
@@ -1255,12 +770,15 @@
       <c r="E7" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" ht="16.8" spans="2:5">
+      <c r="F7" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="3">
         <v>2</v>
       </c>
       <c r="D8" s="4">
@@ -1269,12 +787,15 @@
       <c r="E8" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" ht="16.8" spans="2:5">
+      <c r="F8" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="3">
         <v>1</v>
       </c>
       <c r="D9" s="4">
@@ -1283,12 +804,15 @@
       <c r="E9" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" ht="16.8" spans="2:5">
+      <c r="F9" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="3">
         <v>1</v>
       </c>
       <c r="D10" s="4">
@@ -1297,12 +821,15 @@
       <c r="E10" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" ht="16.8" spans="2:5">
+      <c r="F10" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="3">
         <v>1</v>
       </c>
       <c r="D11" s="4">
@@ -1311,12 +838,15 @@
       <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" ht="16.8" spans="2:5">
+      <c r="F11" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="3">
         <v>1</v>
       </c>
       <c r="D12" s="4">
@@ -1325,12 +855,15 @@
       <c r="E12" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" ht="16.8" spans="2:5">
+      <c r="F12" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="3">
         <v>1</v>
       </c>
       <c r="D13" s="4">
@@ -1339,12 +872,15 @@
       <c r="E13" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" ht="16.8" spans="2:5">
+      <c r="F13" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="3">
         <v>3</v>
       </c>
       <c r="D14" s="4">
@@ -1353,12 +889,15 @@
       <c r="E14" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" ht="16.8" spans="2:5">
+      <c r="F14" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="3">
         <v>1</v>
       </c>
       <c r="D15" s="4">
@@ -1367,12 +906,15 @@
       <c r="E15" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" ht="16.8" spans="2:5">
+      <c r="F15" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="3">
         <v>2</v>
       </c>
       <c r="D16" s="4">
@@ -1381,12 +923,15 @@
       <c r="E16" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" ht="16.8" spans="2:5">
+      <c r="F16" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="14" x14ac:dyDescent="0.35">
       <c r="B17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="4">
@@ -1395,10 +940,13 @@
       <c r="E17" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="F17" s="11" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179DC7D8-EEC3-4F07-A4AF-101509761D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A88607E-6C1B-4B1A-B044-E95DA8AD550D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="1480" windowWidth="18440" windowHeight="13060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31608" yWindow="1008" windowWidth="18444" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
@@ -164,46 +164,47 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>L1_Icon_ChickenLeg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Apple</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Broccoli</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Biscuit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Blueberry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Carrot</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Egg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Salmon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Shrimp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>L1_Icon_Cucumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	L1_Icon_Pumpkin</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_ChickenLeg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Apple</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Broccoli</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Biscuit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Blueberry</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Carrot</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Egg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Salmon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1_Icon_Shrimp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1_Icon_Pumpkin</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +648,7 @@
     <col min="3" max="3" width="16" style="3" customWidth="1"/>
     <col min="4" max="4" width="15" style="4" customWidth="1"/>
     <col min="5" max="5" width="15.7265625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.453125" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -719,7 +720,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -736,7 +737,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
@@ -753,7 +754,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -771,7 +772,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -788,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -805,7 +806,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -822,7 +823,7 @@
         <v>26</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -839,7 +840,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -856,7 +857,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -873,7 +874,7 @@
         <v>32</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -890,7 +891,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -907,7 +908,7 @@
         <v>36</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14" x14ac:dyDescent="0.35">
@@ -924,7 +925,7 @@
         <v>38</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="14" x14ac:dyDescent="0.35">
@@ -941,7 +942,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A88607E-6C1B-4B1A-B044-E95DA8AD550D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70963D34-B1EA-4BD2-BAE4-C9D378250AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31608" yWindow="1008" windowWidth="18444" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5210" yWindow="2610" windowWidth="18440" windowHeight="13060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>

--- a/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/FoodConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70963D34-B1EA-4BD2-BAE4-C9D378250AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5AB0E7-C216-4509-9014-36B82A15FC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5210" yWindow="2610" windowWidth="18440" windowHeight="13060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1131" yWindow="1131" windowWidth="16458" windowHeight="9498" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
@@ -641,18 +641,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.07421875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.61328125" style="3" customWidth="1"/>
     <col min="3" max="3" width="16" style="3" customWidth="1"/>
     <col min="4" max="4" width="15" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="28.453125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.69140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.4609375" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="14.15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -692,7 +692,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="14.15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
@@ -723,7 +723,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
@@ -731,7 +731,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>16</v>
@@ -740,7 +740,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>
@@ -757,7 +757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="A7" s="8"/>
       <c r="B7" s="7" t="s">
         <v>19</v>
@@ -766,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>20</v>
@@ -775,7 +775,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B8" s="7" t="s">
         <v>21</v>
       </c>
@@ -792,7 +792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>24</v>
@@ -809,7 +809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
@@ -826,7 +826,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B11" s="7" t="s">
         <v>27</v>
       </c>
@@ -834,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>28</v>
@@ -843,7 +843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
@@ -860,7 +860,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B13" s="7" t="s">
         <v>31</v>
       </c>
@@ -868,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>32</v>
@@ -877,7 +877,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B14" s="7" t="s">
         <v>33</v>
       </c>
@@ -894,7 +894,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
@@ -902,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>36</v>
@@ -911,7 +911,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B16" s="7" t="s">
         <v>37</v>
       </c>
@@ -928,7 +928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" ht="14.15" x14ac:dyDescent="0.4">
       <c r="B17" s="7" t="s">
         <v>39</v>
       </c>
@@ -936,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>40</v>
